--- a/examples/candidate-rollup/规则_决策表.xlsx
+++ b/examples/candidate-rollup/规则_决策表.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="输入" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="设置" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="变量定义" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="决策表" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="测试" sheetId="4" state="visible" r:id="rId4"/>

--- a/examples/candidate-rollup/规则_决策表.xlsx
+++ b/examples/candidate-rollup/规则_决策表.xlsx
@@ -42,12 +42,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,19 +94,19 @@
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -118,7 +118,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -501,167 +501,179 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="23.6" customWidth="1" min="2" max="2"/>
+    <col width="8.600000000000001" customWidth="1" min="3" max="3"/>
+    <col width="16.2" customWidth="1" min="4" max="4"/>
+    <col width="8.600000000000001" customWidth="1" min="5" max="5"/>
+    <col width="10.8" customWidth="1" min="6" max="6"/>
+    <col width="8.600000000000001" customWidth="1" min="7" max="7"/>
+    <col width="15.8" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>输入表</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>下一行是列名, 之后每行声明一个输入: 名称 = 规则里的前缀; 匹配 = 主表写 主表, 其它写对齐到主表的键; 文件 = 默认文件 (命令行 -i 可覆盖)。输入表下面不要再写别的</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>排序</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>分隔符</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>空值占位</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>带序号</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>岗位</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>岗位清单.xlsx</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="47" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4" ht="47" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>推荐</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>拼接</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>推荐时间 降序</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>推荐记录.xlsx</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>一岗多行: 同一个岗位的推荐记录按 推荐时间 降序 (空值排末尾) 接成一行, 每列各自接; 分隔符留空 = ;。空值占位 NA 让各列按位置对齐 (第 k 个工号对应第 k 个姓名)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>冻结</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>工号 = 岗位.现任工号</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>拼接</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>冻结开始 降序</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>冻结记录.xlsx</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>按 工号 对齐到主表的 现任工号; 带序号 = 1.…;2.…。排序 / 分隔符 / 空值占位 / 带序号 只在 重复键 = 拼接 时允许写</t>
         </is>
@@ -682,34 +694,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="53" customWidth="1" min="2" max="2"/>
+    <col width="56.2" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>变量</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>定义</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="47" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>推荐.现岗</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>拼接(推荐.现部门, "-", 推荐.现岗位, "-", 推荐.职级)</t>
         </is>
@@ -721,12 +733,12 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>冻结.期间</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>拼接(冻结.冻结开始, "~", 冻结.冻结结束)</t>
         </is>
@@ -738,17 +750,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="4" t="n"/>
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="2" t="n"/>
     </row>
     <row r="5" ht="47" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>可用函数</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
+      <c r="B5" s="4" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, ...)  包含 / 不包含 / 开头是 / 开头不是 / 结尾是 / 结尾不是 (x, 文本1, ...)  拼接(a, b, ...)  数字(x)  日期(x)  如果(条件, 真值, 假值)</t>
@@ -769,31 +781,31 @@
   <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10.8" customWidth="1" min="1" max="1"/>
+    <col width="8.600000000000001" customWidth="1" min="2" max="2"/>
+    <col width="11.8" customWidth="1" min="3" max="3"/>
+    <col width="11.8" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="16.2" customWidth="1" min="8" max="8"/>
+    <col width="11.8" customWidth="1" min="9" max="9"/>
+    <col width="16.2" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>两条规则各管各的列, 同时命中互不干扰。聚合发生在匹配层 (输入声明), 规则层仍是逐行</t>
         </is>
@@ -1017,7 +1029,7 @@
           <t>冻结.冻结依据</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>现任者有冻结记录: 带序号 1.…;2.…</t>
         </is>
@@ -1038,20 +1050,20 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="11.8" customWidth="1" min="2" max="2"/>
+    <col width="11.8" customWidth="1" min="3" max="3"/>
+    <col width="17.2" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11.8" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16.2" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="17.2" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
     <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15.8" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -1313,7 +1325,7 @@
       <c r="M4" s="12" t="n"/>
       <c r="N4" s="12" t="n"/>
       <c r="O4" s="12" t="n"/>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>都没有记录, 不动</t>
         </is>
@@ -1363,7 +1375,7 @@
           <t>1.审计;2.纪律</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>只有冻结记录</t>
         </is>
@@ -1445,7 +1457,7 @@
           <t>1.休假</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>两条都命中, 各写各的列</t>
         </is>

--- a/examples/candidate-rollup/规则_决策表.xlsx
+++ b/examples/candidate-rollup/规则_决策表.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,10 +30,17 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font/>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -42,12 +49,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -66,7 +78,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -88,52 +100,107 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -504,7 +571,7 @@
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23.6" customWidth="1" min="2" max="2"/>
     <col width="8.600000000000001" customWidth="1" min="3" max="3"/>
     <col width="16.2" customWidth="1" min="4" max="4"/>
@@ -515,171 +582,181 @@
     <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>输入表</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>下一行是列名, 之后每行声明一个输入: 名称 = 规则里的前缀; 匹配 = 主表写 主表, 其它写对齐到主表的键; 文件 = 默认文件 (命令行 -i 可覆盖)。输入表下面不要再写别的</t>
         </is>
       </c>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>排序</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>分隔符</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>空值占位</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>带序号</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>岗位</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>岗位清单.xlsx</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行</t>
         </is>
       </c>
     </row>
     <row r="4" ht="47" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>推荐</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>拼接</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>推荐时间 降序</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>推荐记录.xlsx</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>一岗多行: 同一个岗位的推荐记录按 推荐时间 降序 (空值排末尾) 接成一行, 每列各自接; 分隔符留空 = ;。空值占位 NA 让各列按位置对齐 (第 k 个工号对应第 k 个姓名)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>冻结</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>工号 = 岗位.现任工号</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>拼接</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>冻结开始 降序</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>冻结记录.xlsx</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>按 工号 对齐到主表的 现任工号; 带序号 = 1.…;2.…。排序 / 分隔符 / 空值占位 / 带序号 只在 重复键 = 拼接 时允许写</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -699,69 +776,69 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>变量</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>定义</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2" ht="47" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>推荐.现岗</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>拼接(推荐.现部门, "-", 推荐.现岗位, "-", 推荐.职级)</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>名字带 推荐. 前缀 = 在推荐记录的每一行上算, 然后才聚合; 只能引用推荐记录自己的列。三列全空为空 (再被占位成 NA), 部分空出 -经理-23级</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>冻结.期间</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>拼接(冻结.冻结开始, "~", 冻结.冻结结束)</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>同上。聚合后是 1.2026-09-01~2026-09-30;2.…。测试用例里这两个变量直接给拼好的文本, 不推导</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n"/>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="2" t="n"/>
+      <c r="A4" s="7" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="9" t="n"/>
     </row>
     <row r="5" ht="47" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>可用函数</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, ...)  包含 / 不包含 / 开头是 / 开头不是 / 结尾是 / 结尾不是 (x, 文本1, ...)  拼接(a, b, ...)  数字(x)  日期(x)  如果(条件, 真值, 假值)</t>
         </is>
@@ -795,247 +872,258 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>两条规则各管各的列, 同时命中互不干扰。聚合发生在匹配层 (输入声明), 规则层仍是逐行</t>
         </is>
       </c>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="K2" s="14" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>推荐.存在</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>冻结.存在</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>拟任人工号</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>拟任人姓名</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>拟任人现岗</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>推荐时间</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>冻结期间</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>冻结依据</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>推荐.工号</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>推荐.姓名</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>推荐.现岗</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>推荐.推荐时间</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>有推荐记录的岗位: 四列都是聚合后的文本 (E2;E1;E3), 输出格直接复制</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>冻结.期间</t>
         </is>
       </c>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t>冻结.冻结依据</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>现任者有冻结记录: 带序号 1.…;2.…</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:K1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1068,396 +1156,396 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="13" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" s="13" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
+      <c r="O1" s="13" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="P1" s="14" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>推荐.存在</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>推荐.工号</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>推荐.姓名</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>推荐.现岗</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>推荐.推荐时间</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>冻结.存在</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>冻结.期间</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>冻结.冻结依据</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>拟任人工号</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="K2" s="13" t="inlineStr">
         <is>
           <t>拟任人姓名</t>
         </is>
       </c>
-      <c r="L2" s="8" t="inlineStr">
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>拟任人现岗</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
+      <c r="M2" s="13" t="inlineStr">
         <is>
           <t>推荐时间</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t>冻结期间</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="O2" s="13" t="inlineStr">
         <is>
           <t>冻结依据</t>
         </is>
       </c>
-      <c r="P2" s="9" t="inlineStr">
+      <c r="P2" s="14" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>E2;E1;E3</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>李四;张三;王五</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>-经理-23级;财务部-会计-22级;人事部-主管-21级</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>2026-10-01;2026-09-01;NA</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="12" t="inlineStr">
+      <c r="H3" s="16" t="n"/>
+      <c r="I3" s="16" t="n"/>
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t>E2;E1;E3</t>
         </is>
       </c>
-      <c r="K3" s="12" t="inlineStr">
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t>李四;张三;王五</t>
         </is>
       </c>
-      <c r="L3" s="14" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>-经理-23级;财务部-会计-22级;人事部-主管-21级</t>
         </is>
       </c>
-      <c r="M3" s="12" t="inlineStr">
+      <c r="M3" s="17" t="inlineStr">
         <is>
           <t>2026-10-01;2026-09-01;NA</t>
         </is>
       </c>
-      <c r="N3" s="12" t="n"/>
-      <c r="O3" s="12" t="n"/>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="N3" s="17" t="n"/>
+      <c r="O3" s="17" t="n"/>
+      <c r="P3" s="10" t="inlineStr">
         <is>
           <t>用例里 推荐.工号 等直接写聚合后的文本; 推荐.现岗 是带前缀的派生变量, 也直接给值</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
-      <c r="I4" s="11" t="n"/>
-      <c r="J4" s="12" t="n"/>
-      <c r="K4" s="12" t="n"/>
-      <c r="L4" s="12" t="n"/>
-      <c r="M4" s="12" t="n"/>
-      <c r="N4" s="12" t="n"/>
-      <c r="O4" s="12" t="n"/>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="H4" s="16" t="n"/>
+      <c r="I4" s="16" t="n"/>
+      <c r="J4" s="17" t="n"/>
+      <c r="K4" s="17" t="n"/>
+      <c r="L4" s="17" t="n"/>
+      <c r="M4" s="17" t="n"/>
+      <c r="N4" s="17" t="n"/>
+      <c r="O4" s="17" t="n"/>
+      <c r="P4" s="9" t="inlineStr">
         <is>
           <t>都没有记录, 不动</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>1.2026-09-01~2026-09-30;2.2026-05-01~2026-05-31</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>1.审计;2.纪律</t>
         </is>
       </c>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
-      <c r="M5" s="12" t="n"/>
-      <c r="N5" s="14" t="inlineStr">
+      <c r="J5" s="17" t="n"/>
+      <c r="K5" s="17" t="n"/>
+      <c r="L5" s="17" t="n"/>
+      <c r="M5" s="17" t="n"/>
+      <c r="N5" s="19" t="inlineStr">
         <is>
           <t>1.2026-09-01~2026-09-30;2.2026-05-01~2026-05-31</t>
         </is>
       </c>
-      <c r="O5" s="12" t="inlineStr">
+      <c r="O5" s="17" t="inlineStr">
         <is>
           <t>1.审计;2.纪律</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P5" s="9" t="inlineStr">
         <is>
           <t>只有冻结记录</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>E5;E6</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>周七;吴八</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>NA;研发部-工程师-20级</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>2026-07-01;2026-06-01</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t>1.2026-08-10~</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>1.休假</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>E5;E6</t>
         </is>
       </c>
-      <c r="K6" s="12" t="inlineStr">
+      <c r="K6" s="17" t="inlineStr">
         <is>
           <t>周七;吴八</t>
         </is>
       </c>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t>NA;研发部-工程师-20级</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr">
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t>2026-07-01;2026-06-01</t>
         </is>
       </c>
-      <c r="N6" s="12" t="inlineStr">
+      <c r="N6" s="17" t="inlineStr">
         <is>
           <t>1.2026-08-10~</t>
         </is>
       </c>
-      <c r="O6" s="12" t="inlineStr">
+      <c r="O6" s="17" t="inlineStr">
         <is>
           <t>1.休假</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="9" t="inlineStr">
         <is>
           <t>两条都命中, 各写各的列</t>
         </is>
